--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432064</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341317</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504715</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432068</v>
+        <v>124432062</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1608,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341322</v>
+        <v>341309</v>
       </c>
       <c r="R10" t="n">
-        <v>6504653</v>
+        <v>6504714</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1687,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432062</v>
+        <v>124432069</v>
       </c>
       <c r="B11" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341309</v>
+        <v>341307</v>
       </c>
       <c r="R11" t="n">
-        <v>6504714</v>
+        <v>6504624</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,21 +1804,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432066</v>
+        <v>124432067</v>
       </c>
       <c r="B12" t="n">
         <v>95089</v>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341335</v>
+        <v>341328</v>
       </c>
       <c r="R12" t="n">
-        <v>6504703</v>
+        <v>6504682</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432059</v>
+        <v>124432068</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1934,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341336</v>
+        <v>341322</v>
       </c>
       <c r="R13" t="n">
-        <v>6504747</v>
+        <v>6504653</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432067</v>
+        <v>124432060</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341328</v>
+        <v>341333</v>
       </c>
       <c r="R14" t="n">
-        <v>6504682</v>
+        <v>6504740</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432060</v>
+        <v>124432065</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,38 +2240,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341333</v>
+        <v>341325</v>
       </c>
       <c r="R16" t="n">
-        <v>6504740</v>
+        <v>6504707</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2314,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432065</v>
+        <v>124432059</v>
       </c>
       <c r="B17" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,39 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341325</v>
+        <v>341336</v>
       </c>
       <c r="R17" t="n">
-        <v>6504707</v>
+        <v>6504747</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2421,21 +2436,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432061</v>
+        <v>124432063</v>
       </c>
       <c r="B18" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,39 +2468,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341321</v>
+        <v>341315</v>
       </c>
       <c r="R18" t="n">
-        <v>6504727</v>
+        <v>6504707</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2543,21 +2538,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2574,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432069</v>
+        <v>124432061</v>
       </c>
       <c r="B19" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,34 +2570,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341307</v>
+        <v>341321</v>
       </c>
       <c r="R19" t="n">
-        <v>6504624</v>
+        <v>6504727</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2660,6 +2645,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432066</v>
+        <v>124432061</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341335</v>
+        <v>341321</v>
       </c>
       <c r="R9" t="n">
-        <v>6504703</v>
+        <v>6504727</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,6 +1585,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432062</v>
+        <v>124432066</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341309</v>
+        <v>341335</v>
       </c>
       <c r="R10" t="n">
-        <v>6504714</v>
+        <v>6504703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432069</v>
+        <v>124432067</v>
       </c>
       <c r="B11" t="n">
         <v>95089</v>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341307</v>
+        <v>341328</v>
       </c>
       <c r="R11" t="n">
-        <v>6504624</v>
+        <v>6504682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432067</v>
+        <v>124432062</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1836,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341328</v>
+        <v>341309</v>
       </c>
       <c r="R12" t="n">
-        <v>6504682</v>
+        <v>6504714</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,6 +1911,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432068</v>
+        <v>124432060</v>
       </c>
       <c r="B13" t="n">
         <v>96729</v>
@@ -1962,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341322</v>
+        <v>341333</v>
       </c>
       <c r="R13" t="n">
-        <v>6504653</v>
+        <v>6504740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432060</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2056,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341333</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504740</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432064</v>
+        <v>124432065</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,38 +2158,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341317</v>
+        <v>341325</v>
       </c>
       <c r="R15" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,6 +2237,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432065</v>
+        <v>124432069</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341325</v>
+        <v>341307</v>
       </c>
       <c r="R16" t="n">
-        <v>6504707</v>
+        <v>6504624</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,21 +2354,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2350,7 +2370,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432059</v>
+        <v>124432063</v>
       </c>
       <c r="B17" t="n">
         <v>95089</v>
@@ -2390,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341336</v>
+        <v>341315</v>
       </c>
       <c r="R17" t="n">
-        <v>6504747</v>
+        <v>6504707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B18" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R18" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432061</v>
+        <v>124432070</v>
       </c>
       <c r="B19" t="n">
-        <v>8361</v>
+        <v>97185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,43 +2586,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106540</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341321</v>
+        <v>341297</v>
       </c>
       <c r="R19" t="n">
-        <v>6504727</v>
+        <v>6504629</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2645,21 +2660,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432070</v>
+        <v>124432068</v>
       </c>
       <c r="B20" t="n">
-        <v>97185</v>
+        <v>96729</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220686</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341297</v>
+        <v>341322</v>
       </c>
       <c r="R20" t="n">
-        <v>6504629</v>
+        <v>6504653</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432061</v>
+        <v>124432063</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341321</v>
+        <v>341315</v>
       </c>
       <c r="R9" t="n">
-        <v>6504727</v>
+        <v>6504707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,7 +1596,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432066</v>
+        <v>124432059</v>
       </c>
       <c r="B10" t="n">
         <v>95089</v>
@@ -1656,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341335</v>
+        <v>341336</v>
       </c>
       <c r="R10" t="n">
-        <v>6504703</v>
+        <v>6504747</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B11" t="n">
         <v>95089</v>
@@ -1758,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R11" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432062</v>
+        <v>124432064</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,43 +1812,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341309</v>
+        <v>341317</v>
       </c>
       <c r="R12" t="n">
-        <v>6504714</v>
+        <v>6504715</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1911,21 +1886,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432060</v>
+        <v>124432065</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,38 +1914,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341333</v>
+        <v>341325</v>
       </c>
       <c r="R13" t="n">
-        <v>6504740</v>
+        <v>6504707</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2028,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2044,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432069</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2084,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341307</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504624</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432065</v>
+        <v>124432062</v>
       </c>
       <c r="B15" t="n">
         <v>8361</v>
@@ -2191,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341325</v>
+        <v>341309</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2268,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432069</v>
+        <v>124432067</v>
       </c>
       <c r="B16" t="n">
         <v>95089</v>
@@ -2308,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341307</v>
+        <v>341328</v>
       </c>
       <c r="R16" t="n">
-        <v>6504624</v>
+        <v>6504682</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432063</v>
+        <v>124432068</v>
       </c>
       <c r="B17" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341315</v>
+        <v>341322</v>
       </c>
       <c r="R17" t="n">
-        <v>6504707</v>
+        <v>6504653</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2472,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432064</v>
+        <v>124432070</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>97185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341317</v>
+        <v>341297</v>
       </c>
       <c r="R18" t="n">
-        <v>6504715</v>
+        <v>6504629</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432070</v>
+        <v>124432060</v>
       </c>
       <c r="B19" t="n">
-        <v>97185</v>
+        <v>96729</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220686</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341297</v>
+        <v>341333</v>
       </c>
       <c r="R19" t="n">
-        <v>6504629</v>
+        <v>6504740</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432068</v>
+        <v>124432061</v>
       </c>
       <c r="B20" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,38 +2668,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341322</v>
+        <v>341321</v>
       </c>
       <c r="R20" t="n">
-        <v>6504653</v>
+        <v>6504727</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2762,6 +2747,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432063</v>
+        <v>124432065</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,31 +1510,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341315</v>
+        <v>341325</v>
       </c>
       <c r="R9" t="n">
         <v>6504707</v>
@@ -1580,6 +1585,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432059</v>
+        <v>124432061</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1632,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341336</v>
+        <v>341321</v>
       </c>
       <c r="R10" t="n">
-        <v>6504747</v>
+        <v>6504727</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1707,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432066</v>
+        <v>124432064</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1750,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341335</v>
+        <v>341317</v>
       </c>
       <c r="R11" t="n">
-        <v>6504703</v>
+        <v>6504715</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432064</v>
+        <v>124432067</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1852,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341317</v>
+        <v>341328</v>
       </c>
       <c r="R12" t="n">
-        <v>6504715</v>
+        <v>6504682</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432065</v>
+        <v>124432062</v>
       </c>
       <c r="B13" t="n">
         <v>8361</v>
@@ -1947,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341325</v>
+        <v>341309</v>
       </c>
       <c r="R13" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2126,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432062</v>
+        <v>124432059</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341309</v>
+        <v>341336</v>
       </c>
       <c r="R15" t="n">
-        <v>6504714</v>
+        <v>6504747</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,21 +2252,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432067</v>
+        <v>124432060</v>
       </c>
       <c r="B16" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341328</v>
+        <v>341333</v>
       </c>
       <c r="R16" t="n">
-        <v>6504682</v>
+        <v>6504740</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2350,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B17" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,25 +2382,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R17" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2554,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432060</v>
+        <v>124432066</v>
       </c>
       <c r="B19" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,25 +2586,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341333</v>
+        <v>341335</v>
       </c>
       <c r="R19" t="n">
-        <v>6504740</v>
+        <v>6504703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2656,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B20" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,43 +2688,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R20" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2747,21 +2762,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1840,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432067</v>
+        <v>124432062</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,34 +1856,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341328</v>
+        <v>341309</v>
       </c>
       <c r="R12" t="n">
-        <v>6504682</v>
+        <v>6504714</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1926,6 +1931,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432062</v>
+        <v>124432067</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,39 +1978,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341309</v>
+        <v>341328</v>
       </c>
       <c r="R13" t="n">
-        <v>6504714</v>
+        <v>6504682</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,21 +2048,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432065</v>
+        <v>124432070</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>97185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,43 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>220686</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341325</v>
+        <v>341297</v>
       </c>
       <c r="R9" t="n">
-        <v>6504707</v>
+        <v>6504629</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1738,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432064</v>
+        <v>124432065</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,38 +1730,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341317</v>
+        <v>341325</v>
       </c>
       <c r="R11" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1824,6 +1809,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1840,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432062</v>
+        <v>124432069</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,39 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341309</v>
+        <v>341307</v>
       </c>
       <c r="R12" t="n">
-        <v>6504714</v>
+        <v>6504624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1931,21 +1926,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1962,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B13" t="n">
         <v>95089</v>
@@ -2002,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R13" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432069</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2104,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341307</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504624</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2166,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432059</v>
+        <v>124432060</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341336</v>
+        <v>341333</v>
       </c>
       <c r="R15" t="n">
-        <v>6504747</v>
+        <v>6504740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2268,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432060</v>
+        <v>124432068</v>
       </c>
       <c r="B16" t="n">
         <v>96729</v>
@@ -2308,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341333</v>
+        <v>341322</v>
       </c>
       <c r="R16" t="n">
-        <v>6504740</v>
+        <v>6504653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B17" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R17" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2472,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432070</v>
+        <v>124432063</v>
       </c>
       <c r="B18" t="n">
-        <v>97185</v>
+        <v>95089</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220686</v>
+        <v>782</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341297</v>
+        <v>341315</v>
       </c>
       <c r="R18" t="n">
-        <v>6504629</v>
+        <v>6504707</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432066</v>
+        <v>124432062</v>
       </c>
       <c r="B19" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,34 +2570,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341335</v>
+        <v>341309</v>
       </c>
       <c r="R19" t="n">
-        <v>6504703</v>
+        <v>6504714</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2660,6 +2645,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432068</v>
+        <v>124432067</v>
       </c>
       <c r="B20" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,25 +2688,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341322</v>
+        <v>341328</v>
       </c>
       <c r="R20" t="n">
-        <v>6504653</v>
+        <v>6504682</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432070</v>
+        <v>124432061</v>
       </c>
       <c r="B9" t="n">
-        <v>97185</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1506,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341297</v>
+        <v>341321</v>
       </c>
       <c r="R9" t="n">
-        <v>6504629</v>
+        <v>6504727</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,6 +1585,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432061</v>
+        <v>124432066</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341321</v>
+        <v>341335</v>
       </c>
       <c r="R10" t="n">
-        <v>6504727</v>
+        <v>6504703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432065</v>
+        <v>124432070</v>
       </c>
       <c r="B11" t="n">
-        <v>8361</v>
+        <v>97185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,43 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341325</v>
+        <v>341297</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504629</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,21 +1804,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1840,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432069</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
         <v>95089</v>
@@ -1880,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341307</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504624</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1942,7 +1922,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432066</v>
+        <v>124432069</v>
       </c>
       <c r="B13" t="n">
         <v>95089</v>
@@ -1982,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341335</v>
+        <v>341307</v>
       </c>
       <c r="R13" t="n">
-        <v>6504703</v>
+        <v>6504624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2044,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432068</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341322</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504653</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,38 +2138,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R15" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,6 +2217,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432068</v>
+        <v>124432065</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,38 +2260,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341322</v>
+        <v>341325</v>
       </c>
       <c r="R16" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,6 +2339,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2350,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432064</v>
+        <v>124432060</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>96729</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341317</v>
+        <v>341333</v>
       </c>
       <c r="R17" t="n">
-        <v>6504715</v>
+        <v>6504740</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2472,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432063</v>
+        <v>124432067</v>
       </c>
       <c r="B18" t="n">
         <v>95089</v>
@@ -2492,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341315</v>
+        <v>341328</v>
       </c>
       <c r="R18" t="n">
-        <v>6504707</v>
+        <v>6504682</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432062</v>
+        <v>124432063</v>
       </c>
       <c r="B19" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,39 +2590,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341309</v>
+        <v>341315</v>
       </c>
       <c r="R19" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2645,21 +2660,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432067</v>
+        <v>124432064</v>
       </c>
       <c r="B20" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,25 +2688,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341328</v>
+        <v>341317</v>
       </c>
       <c r="R20" t="n">
-        <v>6504682</v>
+        <v>6504715</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432061</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341321</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504727</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432066</v>
+        <v>124432060</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341335</v>
+        <v>341333</v>
       </c>
       <c r="R10" t="n">
-        <v>6504703</v>
+        <v>6504740</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432070</v>
+        <v>124432065</v>
       </c>
       <c r="B11" t="n">
-        <v>97185</v>
+        <v>8361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1710,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>106540</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341297</v>
+        <v>341325</v>
       </c>
       <c r="R11" t="n">
-        <v>6504629</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1804,6 +1789,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432061</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1836,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341321</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504727</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,6 +1911,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432069</v>
+        <v>124432062</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,34 +1958,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341307</v>
+        <v>341309</v>
       </c>
       <c r="R13" t="n">
-        <v>6504624</v>
+        <v>6504714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,6 +2033,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B14" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2076,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R14" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432062</v>
+        <v>124432064</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,43 +2178,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341309</v>
+        <v>341317</v>
       </c>
       <c r="R15" t="n">
-        <v>6504714</v>
+        <v>6504715</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,21 +2252,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432065</v>
+        <v>124432059</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341325</v>
+        <v>341336</v>
       </c>
       <c r="R16" t="n">
-        <v>6504707</v>
+        <v>6504747</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2339,21 +2354,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432060</v>
+        <v>124432070</v>
       </c>
       <c r="B17" t="n">
-        <v>96729</v>
+        <v>97185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>220686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341333</v>
+        <v>341297</v>
       </c>
       <c r="R17" t="n">
-        <v>6504740</v>
+        <v>6504629</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432067</v>
+        <v>124432068</v>
       </c>
       <c r="B18" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341328</v>
+        <v>341322</v>
       </c>
       <c r="R18" t="n">
-        <v>6504682</v>
+        <v>6504653</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432063</v>
+        <v>124432067</v>
       </c>
       <c r="B19" t="n">
         <v>95089</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341315</v>
+        <v>341328</v>
       </c>
       <c r="R19" t="n">
-        <v>6504707</v>
+        <v>6504682</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432064</v>
+        <v>124432069</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,25 +2688,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341317</v>
+        <v>341307</v>
       </c>
       <c r="R20" t="n">
-        <v>6504715</v>
+        <v>6504624</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432066</v>
+        <v>124432065</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341335</v>
+        <v>341325</v>
       </c>
       <c r="R9" t="n">
-        <v>6504703</v>
+        <v>6504707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,6 +1585,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432060</v>
+        <v>124432069</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341333</v>
+        <v>341307</v>
       </c>
       <c r="R10" t="n">
-        <v>6504740</v>
+        <v>6504624</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432065</v>
+        <v>124432067</v>
       </c>
       <c r="B11" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341325</v>
+        <v>341328</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1789,21 +1804,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,43 +1832,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R12" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1911,21 +1906,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432062</v>
+        <v>124432060</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,43 +1934,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341309</v>
+        <v>341333</v>
       </c>
       <c r="R13" t="n">
-        <v>6504714</v>
+        <v>6504740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,21 +2008,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2268,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432059</v>
+        <v>124432061</v>
       </c>
       <c r="B16" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,34 +2244,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341336</v>
+        <v>341321</v>
       </c>
       <c r="R16" t="n">
-        <v>6504747</v>
+        <v>6504727</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2354,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2370,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432070</v>
+        <v>124432062</v>
       </c>
       <c r="B17" t="n">
-        <v>97185</v>
+        <v>8361</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,38 +2362,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220686</v>
+        <v>106540</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341297</v>
+        <v>341309</v>
       </c>
       <c r="R17" t="n">
-        <v>6504629</v>
+        <v>6504714</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2456,6 +2441,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432068</v>
+        <v>124432070</v>
       </c>
       <c r="B18" t="n">
-        <v>96729</v>
+        <v>97185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>220686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341322</v>
+        <v>341297</v>
       </c>
       <c r="R18" t="n">
-        <v>6504653</v>
+        <v>6504629</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432067</v>
+        <v>124432059</v>
       </c>
       <c r="B19" t="n">
         <v>95089</v>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341328</v>
+        <v>341336</v>
       </c>
       <c r="R19" t="n">
-        <v>6504682</v>
+        <v>6504747</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432069</v>
+        <v>124432066</v>
       </c>
       <c r="B20" t="n">
         <v>95089</v>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341307</v>
+        <v>341335</v>
       </c>
       <c r="R20" t="n">
-        <v>6504624</v>
+        <v>6504703</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432065</v>
+        <v>124432060</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,43 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341325</v>
+        <v>341333</v>
       </c>
       <c r="R9" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,7 +1596,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432069</v>
+        <v>124432066</v>
       </c>
       <c r="B10" t="n">
         <v>95089</v>
@@ -1656,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341307</v>
+        <v>341335</v>
       </c>
       <c r="R10" t="n">
-        <v>6504624</v>
+        <v>6504703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432067</v>
+        <v>124432063</v>
       </c>
       <c r="B11" t="n">
         <v>95089</v>
@@ -1758,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341328</v>
+        <v>341315</v>
       </c>
       <c r="R11" t="n">
-        <v>6504682</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432068</v>
+        <v>124432070</v>
       </c>
       <c r="B12" t="n">
-        <v>96729</v>
+        <v>97185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>220686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341322</v>
+        <v>341297</v>
       </c>
       <c r="R12" t="n">
-        <v>6504653</v>
+        <v>6504629</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,38 +1914,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R13" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R14" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432064</v>
+        <v>124432065</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,38 +2138,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341317</v>
+        <v>341325</v>
       </c>
       <c r="R15" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,6 +2217,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,43 +2260,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R16" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,21 +2334,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432062</v>
+        <v>124432059</v>
       </c>
       <c r="B17" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,39 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341309</v>
+        <v>341336</v>
       </c>
       <c r="R17" t="n">
-        <v>6504714</v>
+        <v>6504747</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,21 +2436,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2472,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432070</v>
+        <v>124432067</v>
       </c>
       <c r="B18" t="n">
-        <v>97185</v>
+        <v>95089</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220686</v>
+        <v>782</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341297</v>
+        <v>341328</v>
       </c>
       <c r="R18" t="n">
-        <v>6504629</v>
+        <v>6504682</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432059</v>
+        <v>124432061</v>
       </c>
       <c r="B19" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,34 +2570,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341336</v>
+        <v>341321</v>
       </c>
       <c r="R19" t="n">
-        <v>6504747</v>
+        <v>6504727</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2660,6 +2645,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432066</v>
+        <v>124432069</v>
       </c>
       <c r="B20" t="n">
         <v>95089</v>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341335</v>
+        <v>341307</v>
       </c>
       <c r="R20" t="n">
-        <v>6504703</v>
+        <v>6504624</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432060</v>
+        <v>124432061</v>
       </c>
       <c r="B9" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1506,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341333</v>
+        <v>341321</v>
       </c>
       <c r="R9" t="n">
-        <v>6504740</v>
+        <v>6504727</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,6 +1585,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432066</v>
+        <v>124432067</v>
       </c>
       <c r="B10" t="n">
         <v>95089</v>
@@ -1636,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341335</v>
+        <v>341328</v>
       </c>
       <c r="R10" t="n">
-        <v>6504703</v>
+        <v>6504682</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1730,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432070</v>
+        <v>124432069</v>
       </c>
       <c r="B12" t="n">
-        <v>97185</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1832,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220686</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341297</v>
+        <v>341307</v>
       </c>
       <c r="R12" t="n">
-        <v>6504629</v>
+        <v>6504624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432062</v>
+        <v>124432060</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,43 +1934,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341309</v>
+        <v>341333</v>
       </c>
       <c r="R13" t="n">
-        <v>6504714</v>
+        <v>6504740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,21 +2008,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432064</v>
+        <v>124432063</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341317</v>
+        <v>341315</v>
       </c>
       <c r="R14" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432065</v>
+        <v>124432070</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>97185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,43 +2138,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>220686</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341325</v>
+        <v>341297</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504629</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,21 +2212,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432068</v>
+        <v>124432059</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2240,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341322</v>
+        <v>341336</v>
       </c>
       <c r="R16" t="n">
-        <v>6504653</v>
+        <v>6504747</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2350,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432059</v>
+        <v>124432065</v>
       </c>
       <c r="B17" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,34 +2346,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341336</v>
+        <v>341325</v>
       </c>
       <c r="R17" t="n">
-        <v>6504747</v>
+        <v>6504707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2436,6 +2421,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B18" t="n">
         <v>95089</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R18" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B19" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,43 +2566,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R19" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2645,21 +2640,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432069</v>
+        <v>124432062</v>
       </c>
       <c r="B20" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,34 +2672,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341307</v>
+        <v>341309</v>
       </c>
       <c r="R20" t="n">
-        <v>6504624</v>
+        <v>6504714</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2762,6 +2747,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432061</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341321</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504727</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432067</v>
+        <v>124432061</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341328</v>
+        <v>341321</v>
       </c>
       <c r="R10" t="n">
-        <v>6504682</v>
+        <v>6504727</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1702,6 +1687,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1820,7 +1820,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432069</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
         <v>95089</v>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341307</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504624</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432060</v>
+        <v>124432070</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>97185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>220686</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341333</v>
+        <v>341297</v>
       </c>
       <c r="R13" t="n">
-        <v>6504740</v>
+        <v>6504629</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432063</v>
+        <v>124432060</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341315</v>
+        <v>341333</v>
       </c>
       <c r="R14" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432070</v>
+        <v>124432067</v>
       </c>
       <c r="B15" t="n">
-        <v>97185</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220686</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341297</v>
+        <v>341328</v>
       </c>
       <c r="R15" t="n">
-        <v>6504629</v>
+        <v>6504682</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432059</v>
+        <v>124432063</v>
       </c>
       <c r="B16" t="n">
         <v>95089</v>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341336</v>
+        <v>341315</v>
       </c>
       <c r="R16" t="n">
-        <v>6504747</v>
+        <v>6504707</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432065</v>
+        <v>124432062</v>
       </c>
       <c r="B17" t="n">
         <v>8361</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341325</v>
+        <v>341309</v>
       </c>
       <c r="R17" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432066</v>
+        <v>124432065</v>
       </c>
       <c r="B18" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,34 +2468,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341335</v>
+        <v>341325</v>
       </c>
       <c r="R18" t="n">
-        <v>6504703</v>
+        <v>6504707</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,6 +2543,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2554,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432068</v>
+        <v>124432069</v>
       </c>
       <c r="B19" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,25 +2586,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341322</v>
+        <v>341307</v>
       </c>
       <c r="R19" t="n">
-        <v>6504653</v>
+        <v>6504624</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2656,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432062</v>
+        <v>124432068</v>
       </c>
       <c r="B20" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,43 +2688,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341309</v>
+        <v>341322</v>
       </c>
       <c r="R20" t="n">
-        <v>6504714</v>
+        <v>6504653</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2747,21 +2762,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432061</v>
+        <v>124432069</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341321</v>
+        <v>341307</v>
       </c>
       <c r="R10" t="n">
-        <v>6504727</v>
+        <v>6504624</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1682,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1820,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432068</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341322</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504653</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432070</v>
+        <v>124432067</v>
       </c>
       <c r="B13" t="n">
-        <v>97185</v>
+        <v>95089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220686</v>
+        <v>782</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341297</v>
+        <v>341328</v>
       </c>
       <c r="R13" t="n">
-        <v>6504629</v>
+        <v>6504682</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432060</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341333</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504740</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432067</v>
+        <v>124432063</v>
       </c>
       <c r="B15" t="n">
         <v>95089</v>
@@ -2166,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341328</v>
+        <v>341315</v>
       </c>
       <c r="R15" t="n">
-        <v>6504682</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432063</v>
+        <v>124432062</v>
       </c>
       <c r="B16" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,34 +2224,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341315</v>
+        <v>341309</v>
       </c>
       <c r="R16" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2314,6 +2299,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432062</v>
+        <v>124432065</v>
       </c>
       <c r="B17" t="n">
         <v>8361</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341309</v>
+        <v>341325</v>
       </c>
       <c r="R17" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432065</v>
+        <v>124432061</v>
       </c>
       <c r="B18" t="n">
         <v>8361</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341325</v>
+        <v>341321</v>
       </c>
       <c r="R18" t="n">
-        <v>6504707</v>
+        <v>6504727</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432069</v>
+        <v>124432070</v>
       </c>
       <c r="B19" t="n">
-        <v>95089</v>
+        <v>97185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,25 +2586,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>782</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341307</v>
+        <v>341297</v>
       </c>
       <c r="R19" t="n">
-        <v>6504624</v>
+        <v>6504629</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432068</v>
+        <v>124432060</v>
       </c>
       <c r="B20" t="n">
         <v>96729</v>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341322</v>
+        <v>341333</v>
       </c>
       <c r="R20" t="n">
-        <v>6504653</v>
+        <v>6504740</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432066</v>
+        <v>124432063</v>
       </c>
       <c r="B9" t="n">
         <v>95089</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341335</v>
+        <v>341315</v>
       </c>
       <c r="R9" t="n">
-        <v>6504703</v>
+        <v>6504707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432064</v>
+        <v>124432067</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341317</v>
+        <v>341328</v>
       </c>
       <c r="R11" t="n">
-        <v>6504715</v>
+        <v>6504682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432068</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341322</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504653</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432067</v>
+        <v>124432061</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341328</v>
+        <v>341321</v>
       </c>
       <c r="R13" t="n">
-        <v>6504682</v>
+        <v>6504727</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2004,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432066</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2044,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341335</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504703</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432063</v>
+        <v>124432060</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341315</v>
+        <v>341333</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2208,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432062</v>
+        <v>124432070</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>97185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,43 +2240,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>220686</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341309</v>
+        <v>341297</v>
       </c>
       <c r="R16" t="n">
-        <v>6504714</v>
+        <v>6504629</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,21 +2314,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432065</v>
+        <v>124432064</v>
       </c>
       <c r="B17" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,43 +2342,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341325</v>
+        <v>341317</v>
       </c>
       <c r="R17" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2421,21 +2416,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2452,7 +2432,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432061</v>
+        <v>124432065</v>
       </c>
       <c r="B18" t="n">
         <v>8361</v>
@@ -2497,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341321</v>
+        <v>341325</v>
       </c>
       <c r="R18" t="n">
-        <v>6504727</v>
+        <v>6504707</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432070</v>
+        <v>124432068</v>
       </c>
       <c r="B19" t="n">
-        <v>97185</v>
+        <v>96729</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220686</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341297</v>
+        <v>341322</v>
       </c>
       <c r="R19" t="n">
-        <v>6504629</v>
+        <v>6504653</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B20" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,38 +2668,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R20" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2762,6 +2747,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432063</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
         <v>95089</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341315</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504707</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432069</v>
+        <v>124432068</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341307</v>
+        <v>341322</v>
       </c>
       <c r="R10" t="n">
-        <v>6504624</v>
+        <v>6504653</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432067</v>
+        <v>124432060</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341328</v>
+        <v>341333</v>
       </c>
       <c r="R11" t="n">
-        <v>6504682</v>
+        <v>6504740</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432064</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341317</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504715</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432061</v>
+        <v>124432069</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341321</v>
+        <v>341307</v>
       </c>
       <c r="R13" t="n">
-        <v>6504727</v>
+        <v>6504624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,21 +1988,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432066</v>
+        <v>124432067</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2064,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341335</v>
+        <v>341328</v>
       </c>
       <c r="R14" t="n">
-        <v>6504703</v>
+        <v>6504682</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432060</v>
+        <v>124432061</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,38 +2118,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341333</v>
+        <v>341321</v>
       </c>
       <c r="R15" t="n">
-        <v>6504740</v>
+        <v>6504727</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,6 +2197,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432070</v>
+        <v>124432062</v>
       </c>
       <c r="B16" t="n">
-        <v>97185</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,38 +2240,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220686</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341297</v>
+        <v>341309</v>
       </c>
       <c r="R16" t="n">
-        <v>6504629</v>
+        <v>6504714</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2314,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124432064</v>
+        <v>124432070</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>97185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2366,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220686</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>341317</v>
+        <v>341297</v>
       </c>
       <c r="R17" t="n">
-        <v>6504715</v>
+        <v>6504629</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124432065</v>
+        <v>124432059</v>
       </c>
       <c r="B18" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,39 +2468,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>341325</v>
+        <v>341336</v>
       </c>
       <c r="R18" t="n">
-        <v>6504707</v>
+        <v>6504747</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,21 +2538,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B19" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,25 +2566,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R19" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124432062</v>
+        <v>124432065</v>
       </c>
       <c r="B20" t="n">
         <v>8361</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>341309</v>
+        <v>341325</v>
       </c>
       <c r="R20" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 13115-2025 artfynd.xlsx
+++ b/artfynd/A 13115-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/197354</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95993418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432058</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432059</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432066</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432067</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432069</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/430690</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77521996</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77521997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77521999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95993420</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111522829</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432060</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111522845</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432061</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432062</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2737,6 +2837,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432065</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432070</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2936,6 +3046,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95994231</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111522844</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,6 +3250,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432064</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,6 +3352,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432071</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,8 +3454,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124517146</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>